--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  09.06.2025 a 15.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  09.06.2025 a 15.06.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43929320-1D24-4A7D-AC4E-AD7B0A6B7CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710A308E-2F72-4826-9DC3-CA3FB4E10AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,55 @@
     <t>Relatório de Recusas  09.06.2025 a 15.06.2025</t>
   </si>
   <si>
-    <t>132747887</t>
+    <t>132825669</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório Recusas - 11.06.2025</t>
-  </si>
-  <si>
-    <t>132817767</t>
-  </si>
-  <si>
-    <t>132829246</t>
-  </si>
-  <si>
-    <t>132833591</t>
-  </si>
-  <si>
-    <t>132841043</t>
-  </si>
-  <si>
-    <t>132856451</t>
-  </si>
-  <si>
-    <t>132876276</t>
-  </si>
-  <si>
-    <t>132826138</t>
-  </si>
-  <si>
-    <t>132832120</t>
-  </si>
-  <si>
-    <t>132825408</t>
-  </si>
-  <si>
-    <t>132817972</t>
-  </si>
-  <si>
-    <t>132817789</t>
-  </si>
-  <si>
-    <t>132849470</t>
+    <t>Relatório Recusas Santander- 12.06.2025</t>
+  </si>
+  <si>
+    <t>132831501</t>
+  </si>
+  <si>
+    <t>132836021</t>
+  </si>
+  <si>
+    <t>132852923</t>
+  </si>
+  <si>
+    <t>132850480</t>
+  </si>
+  <si>
+    <t>132890543</t>
+  </si>
+  <si>
+    <t>132910572</t>
+  </si>
+  <si>
+    <t>132917618</t>
+  </si>
+  <si>
+    <t>132908319</t>
+  </si>
+  <si>
+    <t>132909899</t>
+  </si>
+  <si>
+    <t>132882888</t>
+  </si>
+  <si>
+    <t>132826001</t>
+  </si>
+  <si>
+    <t>132827355</t>
+  </si>
+  <si>
+    <t>132833720</t>
+  </si>
+  <si>
+    <t>132836068</t>
   </si>
 </sst>
 </file>
@@ -768,11 +774,39 @@
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
